--- a/Cardano/Cardano.xlsx
+++ b/Cardano/Cardano.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/Cardano/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="773" documentId="13_ncr:1_{09A8CA3B-498C-48C2-9132-9CBE0DB7D679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B662B875-8CEB-4376-9EFE-3254651B1C8C}"/>
+  <xr:revisionPtr revIDLastSave="781" documentId="13_ncr:1_{09A8CA3B-498C-48C2-9132-9CBE0DB7D679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A1D97C7-7281-4DC8-9ABD-DFA6E344902C}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5625" yWindow="3690" windowWidth="38880" windowHeight="15345" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MarketCap" sheetId="7" r:id="rId1"/>
@@ -449,6 +449,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2053,7 +2057,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F528616F-4365-4E03-AA99-F5C2282C78C2}">
-  <dimension ref="B1:M21"/>
+  <dimension ref="B1:M22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="46.85546875" customWidth="1"/>
@@ -2382,83 +2386,93 @@
       <c r="B13" s="8"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="8"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
       <c r="K14" s="11"/>
       <c r="M14" s="11"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B15" s="8"/>
+      <c r="B15" s="7"/>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
+      <c r="E15" s="6"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
       <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B16" s="8"/>
+      <c r="B16" s="7"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
+      <c r="E16" s="6"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
       <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="8"/>
+      <c r="B17" s="7"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
+      <c r="E17" s="6"/>
       <c r="F17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="J17" s="11"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="8"/>
+      <c r="B18" s="7"/>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
+      <c r="E18" s="6"/>
       <c r="F18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="J18" s="11"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="8"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
       <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="8"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="H20" s="11"/>
+      <c r="J20" s="11"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="8"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
       <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
       <c r="J21" s="11"/>
       <c r="K21" s="11"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B22" s="8"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="H22" s="11"/>
+      <c r="J22" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
